--- a/data-raw/workbooks/kelpbio-4-canopy-prefit-nereo.xlsx
+++ b/data-raw/workbooks/kelpbio-4-canopy-prefit-nereo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>site</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>Triquetta</t>
+  </si>
+  <si>
+    <t>New site</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -511,6 +514,23 @@
         <v>14926</v>
       </c>
     </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>2026</v>
+      </c>
+      <c r="C8">
+        <v>4732</v>
+      </c>
+      <c r="D8">
+        <v>0.4</v>
+      </c>
+      <c r="E8">
+        <v>9714</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/workbooks/kelpbio-4-canopy-prefit-nereo.xlsx
+++ b/data-raw/workbooks/kelpbio-4-canopy-prefit-nereo.xlsx
@@ -420,13 +420,13 @@
         <v>2026</v>
       </c>
       <c r="C2">
-        <v>4732</v>
+        <v>3651</v>
       </c>
       <c r="D2">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="E2">
-        <v>9714</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -437,13 +437,13 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>10079</v>
+        <v>3130</v>
       </c>
       <c r="D3">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="E3">
-        <v>17722</v>
+        <v>7838</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -454,13 +454,13 @@
         <v>2026</v>
       </c>
       <c r="C4">
-        <v>9744</v>
+        <v>9050</v>
       </c>
       <c r="D4">
         <v>0.35</v>
       </c>
       <c r="E4">
-        <v>19806</v>
+        <v>16269</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -471,13 +471,13 @@
         <v>2026</v>
       </c>
       <c r="C5">
-        <v>4822</v>
+        <v>6658</v>
       </c>
       <c r="D5">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="E5">
-        <v>9712</v>
+        <v>11389</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -488,13 +488,13 @@
         <v>2026</v>
       </c>
       <c r="C6">
-        <v>3191</v>
+        <v>6824</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>9218</v>
+        <v>12134</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -505,13 +505,13 @@
         <v>2026</v>
       </c>
       <c r="C7">
-        <v>6548</v>
+        <v>4924</v>
       </c>
       <c r="D7">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E7">
-        <v>14926</v>
+        <v>12896</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -522,13 +522,13 @@
         <v>2026</v>
       </c>
       <c r="C8">
-        <v>4732</v>
+        <v>3651</v>
       </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="E8">
-        <v>9714</v>
+        <v>5642</v>
       </c>
     </row>
   </sheetData>
